--- a/data/indicadores/05_01_01_04_pgp.xlsx
+++ b/data/indicadores/05_01_01_04_pgp.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BRUNA\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SDSN\Atlas2025\R_codes\Final\Input_indicadores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E35F778-51AC-4EC3-AEFE-83DFA319097E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4DAF42B-9A06-41BF-8520-BA9E60EEC854}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datos Procesados" sheetId="1" r:id="rId1"/>
@@ -23,17 +23,6 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId11" roundtripDataChecksum="WKAjI6B6yWICMmZs2/GTrviTEq/tMjKcV2eNdAOpHhI="/>
     </ext>
@@ -1653,7 +1642,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1727,7 +1716,6 @@
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -2057,10 +2045,10 @@
       <c r="O2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="P2" s="42">
+      <c r="P2" s="41">
         <v>74.226958793553905</v>
       </c>
-      <c r="Q2" s="42">
+      <c r="Q2" s="41">
         <v>80.198514350131305</v>
       </c>
       <c r="R2" s="11">
@@ -2126,10 +2114,10 @@
       <c r="O3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="P3" s="42">
+      <c r="P3" s="41">
         <v>76.228183047939595</v>
       </c>
-      <c r="Q3" s="42">
+      <c r="Q3" s="41">
         <v>81.794084083572599</v>
       </c>
       <c r="R3" s="11">
@@ -2195,10 +2183,10 @@
       <c r="O4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="P4" s="42">
+      <c r="P4" s="41">
         <v>75.887453157620897</v>
       </c>
-      <c r="Q4" s="42">
+      <c r="Q4" s="41">
         <v>80.035483732467597</v>
       </c>
       <c r="R4" s="11">
@@ -2261,10 +2249,10 @@
       <c r="O5" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="P5" s="42">
+      <c r="P5" s="41">
         <v>73.070536759865107</v>
       </c>
-      <c r="Q5" s="42">
+      <c r="Q5" s="41">
         <v>78.660176577208702</v>
       </c>
       <c r="R5" s="11">
@@ -2330,10 +2318,10 @@
       <c r="O6" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="P6" s="42">
+      <c r="P6" s="41">
         <v>76.590396885792899</v>
       </c>
-      <c r="Q6" s="42">
+      <c r="Q6" s="41">
         <v>82.299518183618204</v>
       </c>
       <c r="R6" s="11">
@@ -2399,10 +2387,10 @@
       <c r="O7" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="P7" s="42">
+      <c r="P7" s="41">
         <v>78.403185295785704</v>
       </c>
-      <c r="Q7" s="42">
+      <c r="Q7" s="41">
         <v>80.125061809790694</v>
       </c>
       <c r="R7" s="11">
@@ -2468,10 +2456,10 @@
       <c r="O8" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="P8" s="42">
+      <c r="P8" s="41">
         <v>78.908415062926295</v>
       </c>
-      <c r="Q8" s="42">
+      <c r="Q8" s="41">
         <v>81.654791014419899</v>
       </c>
       <c r="R8" s="11">
@@ -2534,10 +2522,10 @@
       <c r="O9" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="P9" s="42">
+      <c r="P9" s="41">
         <v>77.982164303759006</v>
       </c>
-      <c r="Q9" s="42">
+      <c r="Q9" s="41">
         <v>80.551849681433396</v>
       </c>
       <c r="R9" s="11">
@@ -2600,10 +2588,10 @@
       <c r="O10" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="P10" s="42">
+      <c r="P10" s="41">
         <v>78.609253412226806</v>
       </c>
-      <c r="Q10" s="42">
+      <c r="Q10" s="41">
         <v>81.665780236145096</v>
       </c>
       <c r="R10" s="11">
@@ -2671,7 +2659,7 @@
       <c r="O11" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="P11" s="42">
+      <c r="P11" s="41">
         <v>78.394841232539335</v>
       </c>
       <c r="Q11" s="20">
@@ -2742,7 +2730,7 @@
       <c r="O12" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="P12" s="42">
+      <c r="P12" s="41">
         <v>76.853576222730496</v>
       </c>
       <c r="Q12" s="20">
@@ -18724,10 +18712,10 @@
       <c r="A346" s="15"/>
       <c r="B346" s="5"/>
       <c r="C346" s="5"/>
-      <c r="D346" s="41"/>
-      <c r="E346" s="41"/>
-      <c r="F346" s="41"/>
-      <c r="G346" s="41"/>
+      <c r="D346" s="13"/>
+      <c r="E346" s="13"/>
+      <c r="F346" s="13"/>
+      <c r="G346" s="13"/>
       <c r="H346" s="5"/>
       <c r="I346" s="5"/>
       <c r="J346" s="6"/>
@@ -39767,28 +39755,28 @@
       <c r="B2" s="2" t="s">
         <v>466</v>
       </c>
-      <c r="C2" s="26">
+      <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2">
         <v>1</v>
       </c>
-      <c r="D2" s="26">
-        <v>0.8</v>
-      </c>
-      <c r="E2" s="26">
-        <v>0.8</v>
-      </c>
-      <c r="F2" s="26">
-        <v>0.7</v>
-      </c>
-      <c r="G2" s="26">
-        <v>0.7</v>
-      </c>
-      <c r="H2" s="26">
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>0.75</v>
+      </c>
+      <c r="G2">
+        <v>0.75</v>
+      </c>
+      <c r="H2">
         <v>0.5</v>
       </c>
-      <c r="I2" s="26">
+      <c r="I2">
         <v>0.5</v>
       </c>
-      <c r="J2" s="26">
+      <c r="J2">
         <v>0</v>
       </c>
       <c r="K2" s="14"/>
